--- a/testakten/fluggastrechte-familie-braeutigam/Aufstellung_Auslagen.xlsx
+++ b/testakten/fluggastrechte-familie-braeutigam/Aufstellung_Auslagen.xlsx
@@ -763,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J42"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1514,6 +1514,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="23" t="inlineStr">
         <is>
@@ -1605,6 +1606,7 @@
       <c r="I28" s="25" t="n"/>
       <c r="J28" s="25" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30" ht="22" customHeight="1">
       <c r="B30" s="28" t="inlineStr">
         <is>
@@ -1626,6 +1628,7 @@
       <c r="I30" s="29" t="n"/>
       <c r="J30" s="29" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="23" t="inlineStr">
         <is>
@@ -1787,6 +1790,7 @@
       <c r="I38" s="35" t="n"/>
       <c r="J38" s="36" t="n"/>
     </row>
+    <row r="39"/>
     <row r="40" ht="24" customHeight="1">
       <c r="B40" s="43" t="inlineStr">
         <is>
@@ -1805,10 +1809,11 @@
       <c r="I40" s="44" t="n"/>
       <c r="J40" s="44" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42" ht="32" customHeight="1">
       <c r="B42" s="46" t="inlineStr">
         <is>
-          <t>Hinweis: EUR-Betraege aus Kurs THB/EUR = 38,35 (Stand 13.04.2026). Alle Daten fiktiv (Testakte). Verjaehrung gem. § 195 BGB: 31.12.2029. Verdienstausfall Yasmin noch nicht beziffert (Nachweis Kinderklinik Hamburg ausstehend).</t>
+          <t>Hinweis: EUR-Betraege aus Kurs THB/EUR = 38,35 (Stand 13.04.2026). Beträge nach Belegstand; offene Positionen sind gesondert markiert. Verjaehrung gem. § 195 BGB: 31.12.2029. Verdienstausfall Yasmin noch nicht beziffert (Nachweis Kinderklinik Hamburg ausstehend).</t>
         </is>
       </c>
     </row>
